--- a/6861.T_report.xlsx
+++ b/6861.T_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,58 +449,627 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>手数料込み利益率(%)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>手数料(円)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>決済後資産(円)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>保有日数</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>決済理由</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>バックテスト結果</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="I2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2021-12-17</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2022-01-06</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>70523.59</v>
+      </c>
+      <c r="E2" t="n">
+        <v>67961.73</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-3.63</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-3.83</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1964</v>
+      </c>
+      <c r="I2" t="n">
+        <v>961710</v>
+      </c>
+      <c r="J2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>総取引回数</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
+      <c r="M2" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="3">
-      <c r="I3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2023-03-08</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2023-03-14</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>59879.54</v>
+      </c>
+      <c r="E3" t="n">
+        <v>57630.16</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-3.76</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-3.95</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1887</v>
+      </c>
+      <c r="I3" t="n">
+        <v>923696</v>
+      </c>
+      <c r="J3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>勝率</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>38.5%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="I4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2023-03-23</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2023-04-06</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>60590.83</v>
+      </c>
+      <c r="E4" t="n">
+        <v>58236.67</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-3.89</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-4.08</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1812</v>
+      </c>
+      <c r="I4" t="n">
+        <v>885996</v>
+      </c>
+      <c r="J4" t="n">
+        <v>14</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>総利益率</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>11.04%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="I5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2023-05-08</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2023-05-18</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>62514.35</v>
+      </c>
+      <c r="E5" t="n">
+        <v>67129.87</v>
+      </c>
+      <c r="F5" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1837</v>
+      </c>
+      <c r="I5" t="n">
+        <v>949573</v>
+      </c>
+      <c r="J5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>平均保有日数</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.0日</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>11.6日</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2024-01-10</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2024-02-16</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>63530.22</v>
+      </c>
+      <c r="E6" t="n">
+        <v>67556.86</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1959</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1007799</v>
+      </c>
+      <c r="J6" t="n">
+        <v>37</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>最終資産</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1110433</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>68430.03</v>
+      </c>
+      <c r="E7" t="n">
+        <v>73527</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2091</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1080773</v>
+      </c>
+      <c r="J7" t="n">
+        <v>12</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>手数料込み利益</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>110433</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2024-03-15</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>69640.23</v>
+      </c>
+      <c r="E8" t="n">
+        <v>67478.31</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2128</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1045094</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>総手数料</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>26116</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>71281.5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>75528.07000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2152</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1105202</v>
+      </c>
+      <c r="J9" t="n">
+        <v>15</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>68574.72</v>
+      </c>
+      <c r="E10" t="n">
+        <v>66345.89999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2174</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1067106</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>67724.46000000001</v>
+      </c>
+      <c r="E11" t="n">
+        <v>65586.14</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-3.16</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-3.35</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2101</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1031313</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>61825.02</v>
+      </c>
+      <c r="E12" t="n">
+        <v>59672.95</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-3.48</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-3.68</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2027</v>
+      </c>
+      <c r="I12" t="n">
+        <v>993387</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>59304.2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>56123.01</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-5.36</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-5.56</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1933</v>
+      </c>
+      <c r="I13" t="n">
+        <v>938167</v>
+      </c>
+      <c r="J13" t="n">
+        <v>9</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>61651.59</v>
+      </c>
+      <c r="E14" t="n">
+        <v>73106.82000000001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>18.58</v>
+      </c>
+      <c r="G14" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2051</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1110433</v>
+      </c>
+      <c r="J14" t="n">
+        <v>18</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>take_profit</t>
         </is>
       </c>
     </row>

--- a/6861.T_report.xlsx
+++ b/6861.T_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -533,38 +533,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023-03-08</t>
+          <t>2022-07-29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2023-03-14</t>
+          <t>2022-08-05</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>59879.54</v>
+        <v>51176.05</v>
       </c>
       <c r="E3" t="n">
-        <v>57630.16</v>
+        <v>54473.52</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.76</v>
+        <v>6.44</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.95</v>
+        <v>6.24</v>
       </c>
       <c r="H3" t="n">
-        <v>1887</v>
+        <v>1985</v>
       </c>
       <c r="I3" t="n">
-        <v>923696</v>
+        <v>1021691</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>stop_loss</t>
+          <t>take_profit</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>41.7%</t>
         </is>
       </c>
     </row>
@@ -584,34 +584,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023-03-23</t>
+          <t>2023-03-06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2023-04-06</t>
+          <t>2023-03-14</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>60590.83</v>
+        <v>59664.19</v>
       </c>
       <c r="E4" t="n">
-        <v>58236.67</v>
+        <v>57630.15</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.89</v>
+        <v>-3.41</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.08</v>
+        <v>-3.61</v>
       </c>
       <c r="H4" t="n">
-        <v>1812</v>
+        <v>2009</v>
       </c>
       <c r="I4" t="n">
-        <v>885996</v>
+        <v>984852</v>
       </c>
       <c r="J4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>11.04%</t>
+          <t>7.63%</t>
         </is>
       </c>
     </row>
@@ -635,38 +635,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2023-05-18</t>
+          <t>2023-04-06</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>62514.35</v>
+        <v>60590.83</v>
       </c>
       <c r="E5" t="n">
-        <v>67129.87</v>
+        <v>58236.68</v>
       </c>
       <c r="F5" t="n">
-        <v>7.38</v>
+        <v>-3.89</v>
       </c>
       <c r="G5" t="n">
-        <v>7.18</v>
+        <v>-4.08</v>
       </c>
       <c r="H5" t="n">
-        <v>1837</v>
+        <v>1931</v>
       </c>
       <c r="I5" t="n">
-        <v>949573</v>
+        <v>944656</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>take_profit</t>
+          <t>stop_loss</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>11.6日</t>
+          <t>12.5日</t>
         </is>
       </c>
     </row>
@@ -686,34 +686,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-01-10</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>63530.22</v>
+        <v>62514.35</v>
       </c>
       <c r="E6" t="n">
-        <v>67556.86</v>
+        <v>67129.87</v>
       </c>
       <c r="F6" t="n">
-        <v>6.34</v>
+        <v>7.38</v>
       </c>
       <c r="G6" t="n">
-        <v>6.13</v>
+        <v>7.18</v>
       </c>
       <c r="H6" t="n">
         <v>1959</v>
       </c>
       <c r="I6" t="n">
-        <v>1007799</v>
+        <v>1012442</v>
       </c>
       <c r="J6" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1110433</v>
+        <v>1076324</v>
       </c>
     </row>
     <row r="7">
@@ -735,34 +735,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-01-10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>68430.03</v>
+        <v>63530.22</v>
       </c>
       <c r="E7" t="n">
-        <v>73527</v>
+        <v>67556.86</v>
       </c>
       <c r="F7" t="n">
-        <v>7.45</v>
+        <v>6.34</v>
       </c>
       <c r="G7" t="n">
-        <v>7.24</v>
+        <v>6.13</v>
       </c>
       <c r="H7" t="n">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="I7" t="n">
-        <v>1080773</v>
+        <v>1074523</v>
       </c>
       <c r="J7" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>110433</v>
+        <v>76324</v>
       </c>
     </row>
     <row r="8">
@@ -784,38 +784,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2024-02-22</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>69640.23</v>
+        <v>68430.03</v>
       </c>
       <c r="E8" t="n">
-        <v>67478.31</v>
+        <v>73526.99000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.1</v>
+        <v>7.45</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.3</v>
+        <v>7.24</v>
       </c>
       <c r="H8" t="n">
-        <v>2128</v>
+        <v>2229</v>
       </c>
       <c r="I8" t="n">
-        <v>1045094</v>
+        <v>1152329</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>stop_loss</t>
+          <t>take_profit</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>26116</v>
+        <v>25397</v>
       </c>
     </row>
     <row r="9">
@@ -833,38 +833,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-03-11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>71281.5</v>
+        <v>69640.23</v>
       </c>
       <c r="E9" t="n">
-        <v>75528.07000000001</v>
+        <v>67478.31</v>
       </c>
       <c r="F9" t="n">
-        <v>5.96</v>
+        <v>-3.1</v>
       </c>
       <c r="G9" t="n">
-        <v>5.75</v>
+        <v>-3.3</v>
       </c>
       <c r="H9" t="n">
-        <v>2152</v>
+        <v>2269</v>
       </c>
       <c r="I9" t="n">
-        <v>1105202</v>
+        <v>1114287</v>
       </c>
       <c r="J9" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>take_profit</t>
+          <t>stop_loss</t>
         </is>
       </c>
     </row>
@@ -874,38 +874,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>68574.72</v>
+        <v>71281.5</v>
       </c>
       <c r="E10" t="n">
-        <v>66345.89999999999</v>
+        <v>75528.08</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.25</v>
+        <v>5.96</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.45</v>
+        <v>5.75</v>
       </c>
       <c r="H10" t="n">
-        <v>2174</v>
+        <v>2295</v>
       </c>
       <c r="I10" t="n">
-        <v>1067106</v>
+        <v>1178375</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>stop_loss</t>
+          <t>take_profit</t>
         </is>
       </c>
     </row>
@@ -915,34 +915,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>67724.46000000001</v>
+        <v>66864.31</v>
       </c>
       <c r="E11" t="n">
-        <v>65586.14</v>
+        <v>63790.34</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.16</v>
+        <v>-4.6</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.35</v>
+        <v>-4.79</v>
       </c>
       <c r="H11" t="n">
-        <v>2101</v>
+        <v>2303</v>
       </c>
       <c r="I11" t="n">
-        <v>1031313</v>
+        <v>1121899</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -977,10 +977,10 @@
         <v>-3.68</v>
       </c>
       <c r="H12" t="n">
-        <v>2027</v>
+        <v>2205</v>
       </c>
       <c r="I12" t="n">
-        <v>993387</v>
+        <v>1080642</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -997,79 +997,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>59304.2</v>
+        <v>58178.3</v>
       </c>
       <c r="E13" t="n">
-        <v>56123.01</v>
+        <v>58062.06</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.36</v>
+        <v>-0.2</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.56</v>
+        <v>-0.4</v>
       </c>
       <c r="H13" t="n">
-        <v>1933</v>
+        <v>2159</v>
       </c>
       <c r="I13" t="n">
-        <v>938167</v>
+        <v>1076324</v>
       </c>
       <c r="J13" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>stop_loss</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>61651.59</v>
-      </c>
-      <c r="E14" t="n">
-        <v>73106.82000000001</v>
-      </c>
-      <c r="F14" t="n">
-        <v>18.58</v>
-      </c>
-      <c r="G14" t="n">
-        <v>18.36</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2051</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1110433</v>
-      </c>
-      <c r="J14" t="n">
-        <v>18</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>take_profit</t>
+          <t>atr_stop</t>
         </is>
       </c>
     </row>
